--- a/spec/fixtures/requirements/requirements_test_kit_requirements.xlsx
+++ b/spec/fixtures/requirements/requirements_test_kit_requirements.xlsx
@@ -4329,6 +4329,7 @@
     <hyperlink ref="B8" r:id="rId7" location="must-support" xr:uid="{511CF2D2-1593-984A-B51B-8D4788F9CD6D}"/>
     <hyperlink ref="B10:B12" r:id="rId8" location="prior-authorization-submission" display="https://hl7.org/fhir/us/davinci-pas/STU2/specification.html#prior-authorization-submission" xr:uid="{5609C67B-E64B-2A44-B595-0DE2D1196FE2}"/>
     <hyperlink ref="B9" r:id="rId9" location="must-support" xr:uid="{43A1D511-5248-8F43-A95E-A45E3BDC6EE8}"/>
+    <hyperlink ref="F8" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
